--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R260-HL7Role" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R216-HL7Role" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R260-HL7RoleClass/FHIR/TRE-R260-HL7RoleClass</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R216-HL7RoleCode/FHIR/TRE-R216-HL7RoleCode</t>
   </si>
 </sst>
 </file>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
